--- a/data/output/ALL3_TestRMSE00241/pureComponents_filled_training_predicted_v2.xlsx
+++ b/data/output/ALL3_TestRMSE00241/pureComponents_filled_training_predicted_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\aglotov\Eutectics\data\output\ALL3_TestRMSE00241\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{83FE8914-2D37-4F6C-87CB-A6A04D2A013A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56F84266-CCC7-4A26-8119-4CBD5C31783C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-11625" yWindow="0" windowWidth="21600" windowHeight="14715" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pure Input" sheetId="1" r:id="rId1"/>
@@ -271,7 +271,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
@@ -624,13 +625,17 @@
       <c r="C2" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2">
         <v>420.71209326608653</v>
       </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1">
+      <c r="E2" s="1">
+        <v>24.16708557840721</v>
+      </c>
+      <c r="G2">
         <v>14.10800338024954</v>
+      </c>
+      <c r="H2" s="2">
+        <v>3.7475024298418762</v>
       </c>
       <c r="J2">
         <v>-477.82341122831588</v>
@@ -643,13 +648,17 @@
       <c r="C3" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3">
         <v>375.18552925412422</v>
       </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1">
+      <c r="E3" s="1">
+        <v>18.791194426931671</v>
+      </c>
+      <c r="G3">
         <v>21.4661139671739</v>
+      </c>
+      <c r="H3" s="2">
+        <v>3.901092812902125</v>
       </c>
       <c r="J3">
         <v>-527.23567018829749</v>
@@ -662,13 +671,17 @@
       <c r="C4" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4">
         <v>420.22224386973471</v>
       </c>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1">
+      <c r="E4" s="1">
+        <v>28.322087953978532</v>
+      </c>
+      <c r="G4">
         <v>10.253831318992001</v>
+      </c>
+      <c r="H4" s="2">
+        <v>3.747389995547501</v>
       </c>
       <c r="J4">
         <v>-469.62236037614917</v>
@@ -681,13 +694,17 @@
       <c r="C5" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5">
         <v>490.46208946008568</v>
       </c>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1">
+      <c r="E5" s="1">
+        <v>15.099202064869569</v>
+      </c>
+      <c r="G5">
         <v>49.681324981534537</v>
+      </c>
+      <c r="H5" s="2">
+        <v>3.9010918685871658</v>
       </c>
       <c r="J5">
         <v>-388.25989966336613</v>
@@ -700,13 +717,17 @@
       <c r="C6" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6">
         <v>441.69098459111461</v>
       </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1">
+      <c r="E6" s="1">
+        <v>27.38658721533567</v>
+      </c>
+      <c r="G6">
         <v>41.382345766929497</v>
+      </c>
+      <c r="H6" s="2">
+        <v>7.1513448594094848</v>
       </c>
       <c r="J6">
         <v>-313.6484161775594</v>
@@ -719,13 +740,17 @@
       <c r="C7" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7">
         <v>458.55671584603562</v>
       </c>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1">
+      <c r="E7" s="1">
+        <v>37.012162954142617</v>
+      </c>
+      <c r="G7">
         <v>23.949070849825929</v>
+      </c>
+      <c r="H7" s="2">
+        <v>7.1513917359277439</v>
       </c>
       <c r="J7">
         <v>-1344.7341075197351</v>
@@ -738,13 +763,17 @@
       <c r="C8" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8">
         <v>409.67046805482448</v>
       </c>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1">
+      <c r="E8" s="1">
+        <v>24.285950177756678</v>
+      </c>
+      <c r="G8">
         <v>14.60387762438727</v>
+      </c>
+      <c r="H8" s="2">
+        <v>3.900996019429761</v>
       </c>
       <c r="J8">
         <v>-356.79600304903443</v>
@@ -757,13 +786,17 @@
       <c r="C9" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9">
         <v>532.1067248474651</v>
       </c>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1">
+      <c r="E9" s="1">
+        <v>65.812473315930461</v>
+      </c>
+      <c r="G9">
         <v>9.5051466666829487</v>
+      </c>
+      <c r="H9" s="2">
+        <v>7.1513896754279038</v>
       </c>
       <c r="J9">
         <v>-245.29890973672639</v>
@@ -776,13 +809,17 @@
       <c r="C10" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10">
         <v>571.73086348535026</v>
       </c>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1">
+      <c r="E10" s="1">
+        <v>27.320226553705801</v>
+      </c>
+      <c r="G10">
         <v>19.402393344372651</v>
+      </c>
+      <c r="H10" s="2">
+        <v>3.9010948195706532</v>
       </c>
       <c r="J10">
         <v>-277.08634065221622</v>
@@ -795,13 +832,17 @@
       <c r="C11" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11">
         <v>570.01741558809329</v>
       </c>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1">
+      <c r="E11" s="1">
+        <v>77.707142041612556</v>
+      </c>
+      <c r="G11">
         <v>7.6010829182027164</v>
+      </c>
+      <c r="H11" s="2">
+        <v>7.1513899329904156</v>
       </c>
       <c r="J11">
         <v>-222.23344976406841</v>
@@ -814,13 +855,17 @@
       <c r="C12" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12">
         <v>408.98805428889767</v>
       </c>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1">
+      <c r="E12" s="1">
+        <v>13.805382239121119</v>
+      </c>
+      <c r="G12">
         <v>41.463923001434388</v>
+      </c>
+      <c r="H12" s="2">
+        <v>3.7475208613715871</v>
       </c>
       <c r="J12">
         <v>-441.54072781711858</v>
@@ -833,13 +878,17 @@
       <c r="C13" t="s">
         <v>35</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D13">
         <v>344.00879294413562</v>
       </c>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1">
+      <c r="E13" s="1">
+        <v>48.83665260037516</v>
+      </c>
+      <c r="G13">
         <v>2.8118468411859219</v>
+      </c>
+      <c r="H13" s="2">
+        <v>3.901093757216854</v>
       </c>
       <c r="J13">
         <v>-362.75208486389909</v>
@@ -852,13 +901,17 @@
       <c r="C14" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D14">
         <v>415.21765188173998</v>
       </c>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1">
+      <c r="E14" s="1">
+        <v>14.41469956044916</v>
+      </c>
+      <c r="G14">
         <v>38.890470604936297</v>
+      </c>
+      <c r="H14" s="2">
+        <v>3.7475240561608509</v>
       </c>
       <c r="J14">
         <v>-434.57545345810422</v>
@@ -871,13 +924,17 @@
       <c r="C15" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D15">
         <v>486.27779303735622</v>
       </c>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1">
+      <c r="E15" s="1">
+        <v>37.028169699226822</v>
+      </c>
+      <c r="G15">
         <v>8.151146740771523</v>
+      </c>
+      <c r="H15" s="2">
+        <v>3.9010918685871658</v>
       </c>
       <c r="J15">
         <v>-416.17400778228892</v>
@@ -890,13 +947,17 @@
       <c r="C16" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D16">
         <v>469.45005914284349</v>
       </c>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1">
+      <c r="E16" s="1">
+        <v>12.83809759210431</v>
+      </c>
+      <c r="G16">
         <v>64.199328247814393</v>
+      </c>
+      <c r="H16" s="2">
+        <v>3.901088091325045</v>
       </c>
       <c r="J16">
         <v>-503.27090690316572</v>
@@ -909,13 +970,17 @@
       <c r="C17" t="s">
         <v>43</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D17">
         <v>485.2765046437429</v>
       </c>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1">
+      <c r="E17" s="1">
+        <v>48.070324754805903</v>
+      </c>
+      <c r="G17">
         <v>9.3152418493538516</v>
+      </c>
+      <c r="H17" s="2">
+        <v>5.5276290833018979</v>
       </c>
       <c r="J17">
         <v>-401.73450309748608</v>
@@ -928,13 +993,17 @@
       <c r="C18" t="s">
         <v>45</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D18">
         <v>627.02210726090493</v>
       </c>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1">
+      <c r="E18" s="1">
+        <v>31.717595222514159</v>
+      </c>
+      <c r="G18">
         <v>15.321378863526929</v>
+      </c>
+      <c r="H18" s="2">
+        <v>3.7396050256868549</v>
       </c>
       <c r="J18">
         <v>-207.5696978732104</v>
@@ -947,13 +1016,17 @@
       <c r="C19" t="s">
         <v>47</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D19">
         <v>711.76020400751156</v>
       </c>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1">
+      <c r="E19" s="1">
+        <v>34.110584676336281</v>
+      </c>
+      <c r="G19">
         <v>17.53743284726232</v>
+      </c>
+      <c r="H19" s="2">
+        <v>3.8549497051499908</v>
       </c>
       <c r="J19">
         <v>-223.0018064527053</v>
@@ -966,13 +1039,17 @@
       <c r="C20" t="s">
         <v>49</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D20">
         <v>663.81314930518158</v>
       </c>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1">
+      <c r="E20" s="1">
+        <v>47.215812240533488</v>
+      </c>
+      <c r="G20">
         <v>7.8687263880703391</v>
+      </c>
+      <c r="H20" s="2">
+        <v>3.7983606101455791</v>
       </c>
       <c r="J20">
         <v>-198.26297147332801</v>
@@ -985,13 +1062,17 @@
       <c r="C21" t="s">
         <v>51</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D21">
         <v>837.66435732717241</v>
       </c>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1">
+      <c r="E21" s="1">
+        <v>36.231551338881047</v>
+      </c>
+      <c r="G21">
         <v>20.04615729349738</v>
+      </c>
+      <c r="H21" s="2">
+        <v>3.7963471419849819</v>
       </c>
       <c r="J21">
         <v>-408.56202979795188</v>
@@ -1004,13 +1085,17 @@
       <c r="C22" t="s">
         <v>53</v>
       </c>
-      <c r="D22" s="1">
+      <c r="D22">
         <v>818.92210890690399</v>
       </c>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1">
+      <c r="E22" s="1">
+        <v>32.512790051189107</v>
+      </c>
+      <c r="G22">
         <v>24.71983160790451</v>
+      </c>
+      <c r="H22" s="2">
+        <v>3.8567577884510609</v>
       </c>
       <c r="J22">
         <v>-424.12470222053412</v>
@@ -1023,13 +1108,17 @@
       <c r="C23" t="s">
         <v>55</v>
       </c>
-      <c r="D23" s="1">
+      <c r="D23">
         <v>816.55806318643977</v>
       </c>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1">
+      <c r="E23" s="1">
+        <v>29.713391454215099</v>
+      </c>
+      <c r="G23">
         <v>27.545105986927229</v>
+      </c>
+      <c r="H23" s="2">
+        <v>3.7375670511527002</v>
       </c>
       <c r="J23">
         <v>-420.46927959108319</v>
@@ -1042,13 +1131,17 @@
       <c r="C24" t="s">
         <v>57</v>
       </c>
-      <c r="D24" s="1">
+      <c r="D24">
         <v>265.65914585470381</v>
       </c>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1">
+      <c r="E24" s="1">
+        <v>18.136898851329718</v>
+      </c>
+      <c r="G24">
         <v>11.37924313622762</v>
+      </c>
+      <c r="H24" s="2">
+        <v>3.466149506060634</v>
       </c>
       <c r="J24">
         <v>-160.000875395256</v>
@@ -1061,13 +1154,17 @@
       <c r="C25" t="s">
         <v>59</v>
       </c>
-      <c r="D25" s="1">
+      <c r="D25">
         <v>298.2974595700037</v>
       </c>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1">
+      <c r="E25" s="1">
+        <v>14.30454274584226</v>
+      </c>
+      <c r="G25">
         <v>17.181605140244251</v>
+      </c>
+      <c r="H25" s="2">
+        <v>3.10454022745868</v>
       </c>
       <c r="J25">
         <v>-77.908398381930112</v>
@@ -1080,13 +1177,17 @@
       <c r="C26" t="s">
         <v>61</v>
       </c>
-      <c r="D26" s="1">
+      <c r="D26">
         <v>325.14842603743512</v>
       </c>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1">
+      <c r="E26" s="1">
+        <v>12.835186220901109</v>
+      </c>
+      <c r="G26">
         <v>24.008154781432982</v>
+      </c>
+      <c r="H26" s="2">
+        <v>3.1068071483808928</v>
       </c>
       <c r="J26">
         <v>-83.256931481393764</v>
@@ -1099,13 +1200,17 @@
       <c r="C27" t="s">
         <v>63</v>
       </c>
-      <c r="D27" s="1">
+      <c r="D27">
         <v>346.42515693569447</v>
       </c>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1">
+      <c r="E27" s="1">
+        <v>13.107072202380269</v>
+      </c>
+      <c r="G27">
         <v>31.127658772571269</v>
+      </c>
+      <c r="H27" s="2">
+        <v>3.473133504145733</v>
       </c>
       <c r="J27">
         <v>-121.6470988767424</v>
@@ -1118,13 +1223,17 @@
       <c r="C28" t="s">
         <v>65</v>
       </c>
-      <c r="D28" s="1">
+      <c r="D28">
         <v>211.20695292067521</v>
       </c>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1">
+      <c r="E28" s="1">
+        <v>39.814742480349338</v>
+      </c>
+      <c r="G28">
         <v>4.548552836564614</v>
+      </c>
+      <c r="H28" s="2">
+        <v>5.5736241817472933</v>
       </c>
       <c r="J28">
         <v>-1072.808087383258</v>
@@ -1137,13 +1246,17 @@
       <c r="C29" t="s">
         <v>67</v>
       </c>
-      <c r="D29" s="1">
+      <c r="D29">
         <v>211.20695292067521</v>
       </c>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1">
+      <c r="E29" s="1">
+        <v>39.814742480349338</v>
+      </c>
+      <c r="G29">
         <v>4.548552836564614</v>
+      </c>
+      <c r="H29" s="2">
+        <v>5.5736241817472933</v>
       </c>
       <c r="J29">
         <v>-1072.808087383258</v>
@@ -1156,13 +1269,17 @@
       <c r="C30" t="s">
         <v>69</v>
       </c>
-      <c r="D30" s="1">
+      <c r="D30">
         <v>217.40999069028749</v>
       </c>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1">
+      <c r="E30" s="1">
+        <v>26.34869976392622</v>
+      </c>
+      <c r="G30">
         <v>6.3454365245647084</v>
+      </c>
+      <c r="H30" s="2">
+        <v>4.272068500372467</v>
       </c>
       <c r="J30">
         <v>-39.891824998082647</v>
@@ -1175,13 +1292,17 @@
       <c r="C31" t="s">
         <v>71</v>
       </c>
-      <c r="D31" s="1">
+      <c r="D31">
         <v>244.89794299192451</v>
       </c>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1">
+      <c r="E31" s="1">
+        <v>21.72152194311629</v>
+      </c>
+      <c r="G31">
         <v>8.7943781419063161</v>
+      </c>
+      <c r="H31" s="2">
+        <v>3.8509183528172048</v>
       </c>
       <c r="J31">
         <v>-29.807724307255569</v>

--- a/data/output/ALL3_TestRMSE00241/pureComponents_filled_training_predicted_v2.xlsx
+++ b/data/output/ALL3_TestRMSE00241/pureComponents_filled_training_predicted_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\aglotov\Eutectics\data\output\ALL3_TestRMSE00241\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56F84266-CCC7-4A26-8119-4CBD5C31783C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E051A4FB-E943-434B-81BB-7402012F0DB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-11625" yWindow="0" windowWidth="21600" windowHeight="14715" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pure Input" sheetId="1" r:id="rId1"/>
@@ -271,8 +271,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
@@ -579,6 +578,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="45.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -625,20 +627,25 @@
       <c r="C2" t="s">
         <v>13</v>
       </c>
-      <c r="D2">
-        <v>420.71209326608653</v>
+      <c r="D2" s="1">
+        <v>393.51950362429659</v>
       </c>
       <c r="E2" s="1">
-        <v>24.16708557840721</v>
-      </c>
-      <c r="G2">
-        <v>14.10800338024954</v>
-      </c>
-      <c r="H2" s="2">
-        <v>3.7475024298418762</v>
-      </c>
-      <c r="J2">
-        <v>-477.82341122831588</v>
+        <v>7.6972126434606691</v>
+      </c>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1">
+        <v>13.87355065866041</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0.96412803801941915</v>
+      </c>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1">
+        <v>-477.69878298804218</v>
+      </c>
+      <c r="K2" s="1">
+        <v>11.426816547222311</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -648,20 +655,25 @@
       <c r="C3" t="s">
         <v>15</v>
       </c>
-      <c r="D3">
-        <v>375.18552925412422</v>
+      <c r="D3" s="1">
+        <v>328.85357263563333</v>
       </c>
       <c r="E3" s="1">
-        <v>18.791194426931671</v>
-      </c>
-      <c r="G3">
-        <v>21.4661139671739</v>
-      </c>
-      <c r="H3" s="2">
-        <v>3.901092812902125</v>
-      </c>
-      <c r="J3">
-        <v>-527.23567018829749</v>
+        <v>5.4723051805939171</v>
+      </c>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1">
+        <v>19.980107171804569</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0.96463539856848002</v>
+      </c>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1">
+        <v>-549.35584889503752</v>
+      </c>
+      <c r="K3" s="1">
+        <v>11.42683670100018</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -671,20 +683,25 @@
       <c r="C4" t="s">
         <v>17</v>
       </c>
-      <c r="D4">
-        <v>420.22224386973471</v>
+      <c r="D4" s="1">
+        <v>419.33692022687922</v>
       </c>
       <c r="E4" s="1">
-        <v>28.322087953978532</v>
-      </c>
-      <c r="G4">
-        <v>10.253831318992001</v>
-      </c>
-      <c r="H4" s="2">
-        <v>3.747389995547501</v>
-      </c>
-      <c r="J4">
-        <v>-469.62236037614917</v>
+        <v>9.7862199156999079</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1">
+        <v>9.6272388584894486</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0.96336552561273725</v>
+      </c>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1">
+        <v>-479.21934728054202</v>
+      </c>
+      <c r="K4" s="1">
+        <v>11.42681996956445</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -694,20 +711,25 @@
       <c r="C5" t="s">
         <v>19</v>
       </c>
-      <c r="D5">
-        <v>490.46208946008568</v>
+      <c r="D5" s="1">
+        <v>531.0386917486145</v>
       </c>
       <c r="E5" s="1">
-        <v>15.099202064869569</v>
-      </c>
-      <c r="G5">
-        <v>49.681324981534537</v>
-      </c>
-      <c r="H5" s="2">
-        <v>3.9010918685871658</v>
-      </c>
-      <c r="J5">
-        <v>-388.25989966336613</v>
+        <v>5.2810073587039827</v>
+      </c>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1">
+        <v>51.238158223862648</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0.96488875517406991</v>
+      </c>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1">
+        <v>-396.28166476845661</v>
+      </c>
+      <c r="K5" s="1">
+        <v>11.426840123336291</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -717,20 +739,25 @@
       <c r="C6" t="s">
         <v>21</v>
       </c>
-      <c r="D6">
-        <v>441.69098459111461</v>
+      <c r="D6" s="1">
+        <v>532.80791453720337</v>
       </c>
       <c r="E6" s="1">
-        <v>27.38658721533567</v>
-      </c>
-      <c r="G6">
-        <v>41.382345766929497</v>
-      </c>
-      <c r="H6" s="2">
-        <v>7.1513448594094848</v>
-      </c>
-      <c r="J6">
-        <v>-313.6484161775594</v>
+        <v>36.997063314858629</v>
+      </c>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1">
+        <v>15.415910940454561</v>
+      </c>
+      <c r="H6" s="1">
+        <v>5.0427047180226854</v>
+      </c>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1">
+        <v>-316.18937529641732</v>
+      </c>
+      <c r="K6" s="1">
+        <v>11.42694545473527</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -740,20 +767,25 @@
       <c r="C7" t="s">
         <v>23</v>
       </c>
-      <c r="D7">
-        <v>458.55671584603562</v>
+      <c r="D7" s="1">
+        <v>516.60055014474062</v>
       </c>
       <c r="E7" s="1">
-        <v>37.012162954142617</v>
-      </c>
-      <c r="G7">
-        <v>23.949070849825929</v>
-      </c>
-      <c r="H7" s="2">
-        <v>7.1513917359277439</v>
-      </c>
-      <c r="J7">
-        <v>-1344.7341075197351</v>
+        <v>78.302772378409358</v>
+      </c>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1">
+        <v>10.99472940488357</v>
+      </c>
+      <c r="H7" s="1">
+        <v>9.2454547452705533</v>
+      </c>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1">
+        <v>-394.73690659927757</v>
+      </c>
+      <c r="K7" s="1">
+        <v>22.653569455214971</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -763,20 +795,25 @@
       <c r="C8" t="s">
         <v>25</v>
       </c>
-      <c r="D8">
-        <v>409.67046805482448</v>
+      <c r="D8" s="1">
+        <v>390.7612622134198</v>
       </c>
       <c r="E8" s="1">
-        <v>24.285950177756678</v>
-      </c>
-      <c r="G8">
-        <v>14.60387762438727</v>
-      </c>
-      <c r="H8" s="2">
-        <v>3.900996019429761</v>
-      </c>
-      <c r="J8">
-        <v>-356.79600304903443</v>
+        <v>27.05605801909773</v>
+      </c>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1">
+        <v>42.060316332802032</v>
+      </c>
+      <c r="H8" s="1">
+        <v>7.7048346416088496</v>
+      </c>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1">
+        <v>-400.60628111838832</v>
+      </c>
+      <c r="K8" s="1">
+        <v>21.741682595172001</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -786,20 +823,25 @@
       <c r="C9" t="s">
         <v>27</v>
       </c>
-      <c r="D9">
-        <v>532.1067248474651</v>
+      <c r="D9" s="1">
+        <v>547.25710139016724</v>
       </c>
       <c r="E9" s="1">
-        <v>65.812473315930461</v>
-      </c>
-      <c r="G9">
-        <v>9.5051466666829487</v>
-      </c>
-      <c r="H9" s="2">
-        <v>7.1513896754279038</v>
-      </c>
-      <c r="J9">
-        <v>-245.29890973672639</v>
+        <v>49.873152470389059</v>
+      </c>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1">
+        <v>18.592318559041679</v>
+      </c>
+      <c r="H9" s="1">
+        <v>7.3125176894829984</v>
+      </c>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1">
+        <v>-256.70851113599281</v>
+      </c>
+      <c r="K9" s="1">
+        <v>11.42718995673099</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -809,20 +851,25 @@
       <c r="C10" t="s">
         <v>29</v>
       </c>
-      <c r="D10">
-        <v>571.73086348535026</v>
+      <c r="D10" s="1">
+        <v>639.89744798771005</v>
       </c>
       <c r="E10" s="1">
-        <v>27.320226553705801</v>
-      </c>
-      <c r="G10">
-        <v>19.402393344372651</v>
-      </c>
-      <c r="H10" s="2">
-        <v>3.9010948195706532</v>
-      </c>
-      <c r="J10">
-        <v>-277.08634065221622</v>
+        <v>9.9656198869790789</v>
+      </c>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1">
+        <v>20.494484890362919</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0.96463539856848002</v>
+      </c>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1">
+        <v>-274.85301485117611</v>
+      </c>
+      <c r="K10" s="1">
+        <v>11.42683670100018</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -832,20 +879,25 @@
       <c r="C11" t="s">
         <v>31</v>
       </c>
-      <c r="D11">
-        <v>570.01741558809329</v>
+      <c r="D11" s="1">
+        <v>523.63700877853273</v>
       </c>
       <c r="E11" s="1">
-        <v>77.707142041612556</v>
-      </c>
-      <c r="G11">
-        <v>7.6010829182027164</v>
-      </c>
-      <c r="H11" s="2">
-        <v>7.1513899329904156</v>
-      </c>
-      <c r="J11">
-        <v>-222.23344976406841</v>
+        <v>51.315013805588343</v>
+      </c>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1">
+        <v>17.655383669136722</v>
+      </c>
+      <c r="H11" s="1">
+        <v>7.5936461596750124</v>
+      </c>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1">
+        <v>-199.26632544009121</v>
+      </c>
+      <c r="K11" s="1">
+        <v>11.4269557216428</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -855,20 +907,25 @@
       <c r="C12" t="s">
         <v>33</v>
       </c>
-      <c r="D12">
-        <v>408.98805428889767</v>
+      <c r="D12" s="1">
+        <v>376.40285991518363</v>
       </c>
       <c r="E12" s="1">
-        <v>13.805382239121119</v>
-      </c>
-      <c r="G12">
-        <v>41.463923001434388</v>
-      </c>
-      <c r="H12" s="2">
-        <v>3.7475208613715871</v>
-      </c>
-      <c r="J12">
-        <v>-441.54072781711858</v>
+        <v>4.3387438179315749</v>
+      </c>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1">
+        <v>40.780971154903142</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0.97901202087473083</v>
+      </c>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1">
+        <v>-440.34275085928982</v>
+      </c>
+      <c r="K12" s="1">
+        <v>19.019404213667279</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -878,20 +935,25 @@
       <c r="C13" t="s">
         <v>35</v>
       </c>
-      <c r="D13">
-        <v>344.00879294413562</v>
+      <c r="D13" s="1">
+        <v>293.26423705682629</v>
       </c>
       <c r="E13" s="1">
-        <v>48.83665260037516</v>
-      </c>
-      <c r="G13">
-        <v>2.8118468411859219</v>
-      </c>
-      <c r="H13" s="2">
-        <v>3.901093757216854</v>
-      </c>
-      <c r="J13">
-        <v>-362.75208486389909</v>
+        <v>19.50129986517905</v>
+      </c>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1">
+        <v>1.292538387279009</v>
+      </c>
+      <c r="H13" s="1">
+        <v>0.96463539856848002</v>
+      </c>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1">
+        <v>-502.08588044819999</v>
+      </c>
+      <c r="K13" s="1">
+        <v>19.063526147785229</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -901,20 +963,25 @@
       <c r="C14" t="s">
         <v>37</v>
       </c>
-      <c r="D14">
-        <v>415.21765188173998</v>
+      <c r="D14" s="1">
+        <v>411.76083768240522</v>
       </c>
       <c r="E14" s="1">
-        <v>14.41469956044916</v>
-      </c>
-      <c r="G14">
-        <v>38.890470604936297</v>
-      </c>
-      <c r="H14" s="2">
-        <v>3.7475240561608509</v>
-      </c>
-      <c r="J14">
-        <v>-434.57545345810422</v>
+        <v>4.789352389438414</v>
+      </c>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1">
+        <v>39.310575604446917</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0.97876946288987521</v>
+      </c>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1">
+        <v>-447.25861917389329</v>
+      </c>
+      <c r="K14" s="1">
+        <v>19.019563220853271</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -924,20 +991,25 @@
       <c r="C15" t="s">
         <v>39</v>
       </c>
-      <c r="D15">
-        <v>486.27779303735622</v>
+      <c r="D15" s="1">
+        <v>582.84642176874809</v>
       </c>
       <c r="E15" s="1">
-        <v>37.028169699226822</v>
-      </c>
-      <c r="G15">
-        <v>8.151146740771523</v>
-      </c>
-      <c r="H15" s="2">
-        <v>3.9010918685871658</v>
-      </c>
-      <c r="J15">
-        <v>-416.17400778228892</v>
+        <v>15.344161092929101</v>
+      </c>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1">
+        <v>7.2997386027138003</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0.97998044879148394</v>
+      </c>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1">
+        <v>-441.8953477054676</v>
+      </c>
+      <c r="K15" s="1">
+        <v>11.427064474245149</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
@@ -947,365 +1019,445 @@
       <c r="C16" t="s">
         <v>41</v>
       </c>
-      <c r="D16">
-        <v>469.45005914284349</v>
+      <c r="D16" s="1">
+        <v>473.77023072415852</v>
       </c>
       <c r="E16" s="1">
-        <v>12.83809759210431</v>
-      </c>
-      <c r="G16">
-        <v>64.199328247814393</v>
-      </c>
-      <c r="H16" s="2">
-        <v>3.901088091325045</v>
-      </c>
-      <c r="J16">
-        <v>-503.27090690316572</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+        <v>4.1647856428695293</v>
+      </c>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1">
+        <v>66.569707573696803</v>
+      </c>
+      <c r="H16" s="1">
+        <v>0.96539491130023813</v>
+      </c>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1">
+        <v>-487.51329324898398</v>
+      </c>
+      <c r="K16" s="1">
+        <v>11.426840123336291</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>42</v>
       </c>
       <c r="C17" t="s">
         <v>43</v>
       </c>
-      <c r="D17">
-        <v>485.2765046437429</v>
+      <c r="D17" s="1">
+        <v>648.21909659409926</v>
       </c>
       <c r="E17" s="1">
-        <v>48.070324754805903</v>
-      </c>
-      <c r="G17">
-        <v>9.3152418493538516</v>
-      </c>
-      <c r="H17" s="2">
-        <v>5.5276290833018979</v>
-      </c>
-      <c r="J17">
-        <v>-401.73450309748608</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+        <v>70.772657059693188</v>
+      </c>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1">
+        <v>5.1493107038510182</v>
+      </c>
+      <c r="H17" s="1">
+        <v>4.7487130989179969</v>
+      </c>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1">
+        <v>-395.11122515179369</v>
+      </c>
+      <c r="K17" s="1">
+        <v>11.42682339190557</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>44</v>
       </c>
       <c r="C18" t="s">
         <v>45</v>
       </c>
-      <c r="D18">
-        <v>627.02210726090493</v>
+      <c r="D18" s="1">
+        <v>674.59943309223604</v>
       </c>
       <c r="E18" s="1">
-        <v>31.717595222514159</v>
-      </c>
-      <c r="G18">
-        <v>15.321378863526929</v>
-      </c>
-      <c r="H18" s="2">
-        <v>3.7396050256868549</v>
-      </c>
-      <c r="J18">
-        <v>-207.5696978732104</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+        <v>11.882496825511859</v>
+      </c>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1">
+        <v>16.011172051126419</v>
+      </c>
+      <c r="H18" s="1">
+        <v>0.97165553020041906</v>
+      </c>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1">
+        <v>-191.89822977109321</v>
+      </c>
+      <c r="K18" s="1">
+        <v>11.426935187818509</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>46</v>
       </c>
       <c r="C19" t="s">
         <v>47</v>
       </c>
-      <c r="D19">
-        <v>711.76020400751156</v>
+      <c r="D19" s="1">
+        <v>875.91182659417757</v>
       </c>
       <c r="E19" s="1">
-        <v>34.110584676336281</v>
-      </c>
-      <c r="G19">
-        <v>17.53743284726232</v>
-      </c>
-      <c r="H19" s="2">
-        <v>3.8549497051499908</v>
-      </c>
-      <c r="J19">
-        <v>-223.0018064527053</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+        <v>13.982347021400329</v>
+      </c>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1">
+        <v>19.184611539407431</v>
+      </c>
+      <c r="H19" s="1">
+        <v>0.97264607244303469</v>
+      </c>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1">
+        <v>-226.88021167970791</v>
+      </c>
+      <c r="K19" s="1">
+        <v>11.426942032430709</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>48</v>
       </c>
       <c r="C20" t="s">
         <v>49</v>
       </c>
-      <c r="D20">
-        <v>663.81314930518158</v>
+      <c r="D20" s="1">
+        <v>558.88226141766097</v>
       </c>
       <c r="E20" s="1">
-        <v>47.215812240533488</v>
-      </c>
-      <c r="G20">
-        <v>7.8687263880703391</v>
-      </c>
-      <c r="H20" s="2">
-        <v>3.7983606101455791</v>
-      </c>
-      <c r="J20">
-        <v>-198.26297147332801</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+        <v>14.909252574565789</v>
+      </c>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1">
+        <v>7.139223883380172</v>
+      </c>
+      <c r="H20" s="1">
+        <v>0.97828381359695016</v>
+      </c>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1">
+        <v>-190.43206693980471</v>
+      </c>
+      <c r="K20" s="1">
+        <v>11.427098316627029</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>50</v>
       </c>
       <c r="C21" t="s">
         <v>51</v>
       </c>
-      <c r="D21">
-        <v>837.66435732717241</v>
+      <c r="D21" s="1">
+        <v>882.77793709994944</v>
       </c>
       <c r="E21" s="1">
-        <v>36.231551338881047</v>
-      </c>
-      <c r="G21">
-        <v>20.04615729349738</v>
-      </c>
-      <c r="H21" s="2">
-        <v>3.7963471419849819</v>
-      </c>
-      <c r="J21">
-        <v>-408.56202979795188</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+        <v>13.80584578564193</v>
+      </c>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1">
+        <v>19.913173255621029</v>
+      </c>
+      <c r="H21" s="1">
+        <v>0.96488875517406991</v>
+      </c>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1">
+        <v>-408.55818441721181</v>
+      </c>
+      <c r="K21" s="1">
+        <v>11.42683670100018</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>52</v>
       </c>
       <c r="C22" t="s">
         <v>53</v>
       </c>
-      <c r="D22">
-        <v>818.92210890690399</v>
+      <c r="D22" s="1">
+        <v>1047.2792898697619</v>
       </c>
       <c r="E22" s="1">
-        <v>32.512790051189107</v>
-      </c>
-      <c r="G22">
-        <v>24.71983160790451</v>
-      </c>
-      <c r="H22" s="2">
-        <v>3.8567577884510609</v>
-      </c>
-      <c r="J22">
-        <v>-424.12470222053412</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+        <v>14.29134448959716</v>
+      </c>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1">
+        <v>26.335883289276818</v>
+      </c>
+      <c r="H22" s="1">
+        <v>0.99347867540190515</v>
+      </c>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1">
+        <v>-436.59221331556932</v>
+      </c>
+      <c r="K22" s="1">
+        <v>11.42732950684694</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>54</v>
       </c>
       <c r="C23" t="s">
         <v>55</v>
       </c>
-      <c r="D23">
-        <v>816.55806318643977</v>
+      <c r="D23" s="1">
+        <v>1070.1451925809181</v>
       </c>
       <c r="E23" s="1">
-        <v>29.713391454215099</v>
-      </c>
-      <c r="G23">
-        <v>27.545105986927229</v>
-      </c>
-      <c r="H23" s="2">
-        <v>3.7375670511527002</v>
-      </c>
-      <c r="J23">
-        <v>-420.46927959108319</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+        <v>13.501391948855151</v>
+      </c>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1">
+        <v>30.35386218309965</v>
+      </c>
+      <c r="H23" s="1">
+        <v>0.96412803801941915</v>
+      </c>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1">
+        <v>-411.09777671955612</v>
+      </c>
+      <c r="K23" s="1">
+        <v>11.42682339190557</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>56</v>
       </c>
       <c r="C24" t="s">
         <v>57</v>
       </c>
-      <c r="D24">
-        <v>265.65914585470381</v>
+      <c r="D24" s="1">
+        <v>245.39073600794771</v>
       </c>
       <c r="E24" s="1">
-        <v>18.136898851329718</v>
-      </c>
-      <c r="G24">
-        <v>11.37924313622762</v>
-      </c>
-      <c r="H24" s="2">
-        <v>3.466149506060634</v>
-      </c>
-      <c r="J24">
-        <v>-160.000875395256</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+        <v>5.7988724005553447</v>
+      </c>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1">
+        <v>10.944381665993751</v>
+      </c>
+      <c r="H24" s="1">
+        <v>0.96991476026174228</v>
+      </c>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1">
+        <v>-23.840497119426121</v>
+      </c>
+      <c r="K24" s="1">
+        <v>11.94127219387849</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>58</v>
       </c>
       <c r="C25" t="s">
         <v>59</v>
       </c>
-      <c r="D25">
-        <v>298.2974595700037</v>
+      <c r="D25" s="1">
+        <v>279.465336423037</v>
       </c>
       <c r="E25" s="1">
-        <v>14.30454274584226</v>
-      </c>
-      <c r="G25">
-        <v>17.181605140244251</v>
-      </c>
-      <c r="H25" s="2">
-        <v>3.10454022745868</v>
-      </c>
-      <c r="J25">
-        <v>-77.908398381930112</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+        <v>5.3875798126864964</v>
+      </c>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1">
+        <v>15.33108722647065</v>
+      </c>
+      <c r="H25" s="1">
+        <v>0.94530532993472216</v>
+      </c>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1">
+        <v>-29.02612087697651</v>
+      </c>
+      <c r="K25" s="1">
+        <v>12.93393869209021</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>60</v>
       </c>
       <c r="C26" t="s">
         <v>61</v>
       </c>
-      <c r="D26">
-        <v>325.14842603743512</v>
+      <c r="D26" s="1">
+        <v>307.76712547266197</v>
       </c>
       <c r="E26" s="1">
-        <v>12.835186220901109</v>
-      </c>
-      <c r="G26">
-        <v>24.008154781432982</v>
-      </c>
-      <c r="H26" s="2">
-        <v>3.1068071483808928</v>
-      </c>
-      <c r="J26">
-        <v>-83.256931481393764</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+        <v>4.7279662609797564</v>
+      </c>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1">
+        <v>23.60231617822987</v>
+      </c>
+      <c r="H26" s="1">
+        <v>0.9514401569656239</v>
+      </c>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1">
+        <v>-40.992148096516871</v>
+      </c>
+      <c r="K26" s="1">
+        <v>14.813645493734329</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>62</v>
       </c>
       <c r="C27" t="s">
         <v>63</v>
       </c>
-      <c r="D27">
-        <v>346.42515693569447</v>
+      <c r="D27" s="1">
+        <v>323.45958670506423</v>
       </c>
       <c r="E27" s="1">
-        <v>13.107072202380269</v>
-      </c>
-      <c r="G27">
-        <v>31.127658772571269</v>
-      </c>
-      <c r="H27" s="2">
-        <v>3.473133504145733</v>
-      </c>
-      <c r="J27">
-        <v>-121.6470988767424</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+        <v>4.3944025320902629</v>
+      </c>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1">
+        <v>30.71074486824374</v>
+      </c>
+      <c r="H27" s="1">
+        <v>0.9871537645846763</v>
+      </c>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1">
+        <v>-53.2246903340166</v>
+      </c>
+      <c r="K27" s="1">
+        <v>16.11022748759359</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>64</v>
       </c>
       <c r="C28" t="s">
         <v>65</v>
       </c>
-      <c r="D28">
-        <v>211.20695292067521</v>
+      <c r="D28" s="1">
+        <v>384.48568131790302</v>
       </c>
       <c r="E28" s="1">
-        <v>39.814742480349338</v>
-      </c>
-      <c r="G28">
-        <v>4.548552836564614</v>
-      </c>
-      <c r="H28" s="2">
-        <v>5.5736241817472933</v>
-      </c>
-      <c r="J28">
-        <v>-1072.808087383258</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+        <v>65.698473398460322</v>
+      </c>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1">
+        <v>6.8704571063808721</v>
+      </c>
+      <c r="H28" s="1">
+        <v>7.6493433744123447</v>
+      </c>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1">
+        <v>-137.97643128377041</v>
+      </c>
+      <c r="K28" s="1">
+        <v>18.34818092002206</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>66</v>
       </c>
       <c r="C29" t="s">
         <v>67</v>
       </c>
-      <c r="D29">
-        <v>211.20695292067521</v>
+      <c r="D29" s="1">
+        <v>384.48568131790302</v>
       </c>
       <c r="E29" s="1">
-        <v>39.814742480349338</v>
-      </c>
-      <c r="G29">
-        <v>4.548552836564614</v>
-      </c>
-      <c r="H29" s="2">
-        <v>5.5736241817472933</v>
-      </c>
-      <c r="J29">
-        <v>-1072.808087383258</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+        <v>65.698473398460322</v>
+      </c>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1">
+        <v>6.8704571063808721</v>
+      </c>
+      <c r="H29" s="1">
+        <v>7.6493433744123447</v>
+      </c>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1">
+        <v>-137.97643128377041</v>
+      </c>
+      <c r="K29" s="1">
+        <v>18.34818092002206</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>68</v>
       </c>
       <c r="C30" t="s">
         <v>69</v>
       </c>
-      <c r="D30">
-        <v>217.40999069028749</v>
+      <c r="D30" s="1">
+        <v>177.60503338668681</v>
       </c>
       <c r="E30" s="1">
-        <v>26.34869976392622</v>
-      </c>
-      <c r="G30">
-        <v>6.3454365245647084</v>
-      </c>
-      <c r="H30" s="2">
-        <v>4.272068500372467</v>
-      </c>
-      <c r="J30">
-        <v>-39.891824998082647</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+        <v>6.1100965853665068</v>
+      </c>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1">
+        <v>5.9078410766219811</v>
+      </c>
+      <c r="H30" s="1">
+        <v>0.955899462600454</v>
+      </c>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1">
+        <v>-21.468315320080649</v>
+      </c>
+      <c r="K30" s="1">
+        <v>11.42681996956445</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>70</v>
       </c>
       <c r="C31" t="s">
         <v>71</v>
       </c>
-      <c r="D31">
-        <v>244.89794299192451</v>
+      <c r="D31" s="1">
+        <v>154.26991851913741</v>
       </c>
       <c r="E31" s="1">
-        <v>21.72152194311629</v>
-      </c>
-      <c r="G31">
-        <v>8.7943781419063161</v>
-      </c>
-      <c r="H31" s="2">
-        <v>3.8509183528172048</v>
-      </c>
-      <c r="J31">
-        <v>-29.807724307255569</v>
+        <v>5.2687387092429949</v>
+      </c>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1">
+        <v>6.5727602652564681</v>
+      </c>
+      <c r="H31" s="1">
+        <v>0.96336552561273725</v>
+      </c>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1">
+        <v>-27.18008637277029</v>
+      </c>
+      <c r="K31" s="1">
+        <v>11.426809702534941</v>
       </c>
     </row>
   </sheetData>
